--- a/plot/data/source_data/source_data_fig_2_b.xlsx
+++ b/plot/data/source_data/source_data_fig_2_b.xlsx
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="E187" s="2" t="n">
-        <v>66.66666666666667</v>
+        <v>66</v>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
@@ -9165,19 +9165,19 @@
         <v>2.352352732274996</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>65.75714285714284</v>
+        <v>65.74761904761903</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>2.513039378862724</v>
+        <v>2.51080480857224</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.8333333333333286</v>
+        <v>0.8428571428571416</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.0269553839796889</v>
+        <v>0.0368612807908141</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1.639711282686968</v>
+        <v>1.648853004923469</v>
       </c>
     </row>
   </sheetData>
